--- a/excel_reports/backtest_compare/s16/compare_s16_M15_20260528_0800_20260608_1000.xlsx
+++ b/excel_reports/backtest_compare/s16/compare_s16_M15_20260528_0800_20260608_1000.xlsx
@@ -16,12 +16,12 @@
     <sheet name="Gap Summary" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Compare'!$A$1:$BK$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Compare'!$A$1:$BK$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Mismatches'!$A$1:$BK$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Live Only'!$A$1:$BK$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Backtest Only'!$A$1:$BK$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Backtest Only'!$A$1:$BK$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Matches'!$A$1:$BK$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Gap Summary'!$A$1:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Gap Summary'!$A$1:$G$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -29,9 +29,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -62,11 +60,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00E2F0D9"/>
       </patternFill>
     </fill>
@@ -78,6 +71,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F8CBAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -93,27 +91,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -508,7 +497,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-09 15:30:30</t>
+          <t>2026-06-18 17:09:51</t>
         </is>
       </c>
     </row>
@@ -671,7 +660,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -770,11 +759,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK3"/>
+  <dimension ref="A1:BK2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -802,8 +791,8 @@
     <col width="34" customWidth="1" min="27" max="27"/>
     <col width="29" customWidth="1" min="28" max="28"/>
     <col width="22" customWidth="1" min="29" max="29"/>
-    <col width="21" customWidth="1" min="30" max="30"/>
-    <col width="21" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="13" customWidth="1" min="31" max="31"/>
     <col width="16" customWidth="1" min="32" max="32"/>
     <col width="10" customWidth="1" min="33" max="33"/>
     <col width="10" customWidth="1" min="34" max="34"/>
@@ -1156,16 +1145,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>NO_SAME_SIDE_CANDIDATE</t>
-        </is>
-      </c>
+      <c r="A2" s="8" t="inlineStr"/>
+      <c r="B2" s="8" t="inlineStr"/>
       <c r="C2" s="8" t="inlineStr"/>
       <c r="D2" s="8" t="inlineStr"/>
       <c r="E2" s="8" t="inlineStr"/>
@@ -1193,35 +1174,17 @@
       <c r="AA2" s="8" t="inlineStr"/>
       <c r="AB2" s="8" t="inlineStr"/>
       <c r="AC2" s="8" t="inlineStr"/>
-      <c r="AD2" s="9" t="n">
-        <v>46171.63541666666</v>
-      </c>
-      <c r="AE2" s="9" t="n">
-        <v>46171.72916666666</v>
-      </c>
-      <c r="AF2" s="8" t="n">
-        <v>4542.18</v>
-      </c>
-      <c r="AG2" s="8" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="AH2" s="8" t="n">
-        <v>4517.1</v>
-      </c>
-      <c r="AI2" s="8" t="n">
-        <v>-25.08</v>
-      </c>
+      <c r="AD2" s="8" t="inlineStr"/>
+      <c r="AE2" s="8" t="inlineStr"/>
+      <c r="AF2" s="8" t="inlineStr"/>
+      <c r="AG2" s="8" t="inlineStr"/>
+      <c r="AH2" s="8" t="inlineStr"/>
+      <c r="AI2" s="8" t="inlineStr"/>
       <c r="AJ2" s="8" t="inlineStr"/>
       <c r="AK2" s="8" t="inlineStr"/>
       <c r="AL2" s="8" t="inlineStr"/>
       <c r="AM2" s="8" t="inlineStr"/>
-      <c r="AN2" s="8" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
+      <c r="AN2" s="8" t="inlineStr"/>
       <c r="AO2" s="8" t="inlineStr"/>
       <c r="AP2" s="8" t="inlineStr"/>
       <c r="AQ2" s="8" t="inlineStr"/>
@@ -1246,99 +1209,8 @@
       <c r="BJ2" s="8" t="inlineStr"/>
       <c r="BK2" s="8" t="inlineStr"/>
     </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>NO_SAME_SIDE_CANDIDATE</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr"/>
-      <c r="D3" s="8" t="inlineStr"/>
-      <c r="E3" s="8" t="inlineStr"/>
-      <c r="F3" s="8" t="inlineStr"/>
-      <c r="G3" s="8" t="inlineStr"/>
-      <c r="H3" s="8" t="inlineStr"/>
-      <c r="I3" s="8" t="inlineStr"/>
-      <c r="J3" s="8" t="inlineStr"/>
-      <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="8" t="inlineStr"/>
-      <c r="M3" s="8" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr"/>
-      <c r="O3" s="8" t="inlineStr"/>
-      <c r="P3" s="8" t="inlineStr"/>
-      <c r="Q3" s="8" t="inlineStr"/>
-      <c r="R3" s="8" t="inlineStr"/>
-      <c r="S3" s="8" t="inlineStr"/>
-      <c r="T3" s="8" t="inlineStr"/>
-      <c r="U3" s="8" t="inlineStr"/>
-      <c r="V3" s="8" t="inlineStr"/>
-      <c r="W3" s="8" t="inlineStr"/>
-      <c r="X3" s="8" t="inlineStr"/>
-      <c r="Y3" s="8" t="inlineStr"/>
-      <c r="Z3" s="8" t="inlineStr"/>
-      <c r="AA3" s="8" t="inlineStr"/>
-      <c r="AB3" s="8" t="inlineStr"/>
-      <c r="AC3" s="8" t="inlineStr"/>
-      <c r="AD3" s="9" t="n">
-        <v>46178.91666666666</v>
-      </c>
-      <c r="AE3" s="9" t="n">
-        <v>46179.09375</v>
-      </c>
-      <c r="AF3" s="8" t="n">
-        <v>4314.33</v>
-      </c>
-      <c r="AG3" s="8" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH3" s="8" t="n">
-        <v>4363.91</v>
-      </c>
-      <c r="AI3" s="8" t="n">
-        <v>-49.58</v>
-      </c>
-      <c r="AJ3" s="8" t="inlineStr"/>
-      <c r="AK3" s="8" t="inlineStr"/>
-      <c r="AL3" s="8" t="inlineStr"/>
-      <c r="AM3" s="8" t="inlineStr"/>
-      <c r="AN3" s="8" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO3" s="8" t="inlineStr"/>
-      <c r="AP3" s="8" t="inlineStr"/>
-      <c r="AQ3" s="8" t="inlineStr"/>
-      <c r="AR3" s="8" t="inlineStr"/>
-      <c r="AS3" s="8" t="inlineStr"/>
-      <c r="AT3" s="8" t="inlineStr"/>
-      <c r="AU3" s="8" t="inlineStr"/>
-      <c r="AV3" s="8" t="inlineStr"/>
-      <c r="AW3" s="8" t="inlineStr"/>
-      <c r="AX3" s="8" t="inlineStr"/>
-      <c r="AY3" s="8" t="inlineStr"/>
-      <c r="AZ3" s="8" t="inlineStr"/>
-      <c r="BA3" s="8" t="inlineStr"/>
-      <c r="BB3" s="8" t="inlineStr"/>
-      <c r="BC3" s="8" t="inlineStr"/>
-      <c r="BD3" s="8" t="inlineStr"/>
-      <c r="BE3" s="8" t="inlineStr"/>
-      <c r="BF3" s="8" t="inlineStr"/>
-      <c r="BG3" s="8" t="inlineStr"/>
-      <c r="BH3" s="8" t="inlineStr"/>
-      <c r="BI3" s="8" t="inlineStr"/>
-      <c r="BJ3" s="8" t="inlineStr"/>
-      <c r="BK3" s="8" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BK3"/>
+  <autoFilter ref="A1:BK2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1735,69 +1607,69 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr"/>
-      <c r="B2" s="10" t="inlineStr"/>
-      <c r="C2" s="10" t="inlineStr"/>
-      <c r="D2" s="10" t="inlineStr"/>
-      <c r="E2" s="10" t="inlineStr"/>
-      <c r="F2" s="10" t="inlineStr"/>
-      <c r="G2" s="10" t="inlineStr"/>
-      <c r="H2" s="10" t="inlineStr"/>
-      <c r="I2" s="10" t="inlineStr"/>
-      <c r="J2" s="10" t="inlineStr"/>
-      <c r="K2" s="10" t="inlineStr"/>
-      <c r="L2" s="10" t="inlineStr"/>
-      <c r="M2" s="10" t="inlineStr"/>
-      <c r="N2" s="10" t="inlineStr"/>
-      <c r="O2" s="10" t="inlineStr"/>
-      <c r="P2" s="10" t="inlineStr"/>
-      <c r="Q2" s="10" t="inlineStr"/>
-      <c r="R2" s="10" t="inlineStr"/>
-      <c r="S2" s="10" t="inlineStr"/>
-      <c r="T2" s="10" t="inlineStr"/>
-      <c r="U2" s="10" t="inlineStr"/>
-      <c r="V2" s="10" t="inlineStr"/>
-      <c r="W2" s="10" t="inlineStr"/>
-      <c r="X2" s="10" t="inlineStr"/>
-      <c r="Y2" s="10" t="inlineStr"/>
-      <c r="Z2" s="10" t="inlineStr"/>
-      <c r="AA2" s="10" t="inlineStr"/>
-      <c r="AB2" s="10" t="inlineStr"/>
-      <c r="AC2" s="10" t="inlineStr"/>
-      <c r="AD2" s="10" t="inlineStr"/>
-      <c r="AE2" s="10" t="inlineStr"/>
-      <c r="AF2" s="10" t="inlineStr"/>
-      <c r="AG2" s="10" t="inlineStr"/>
-      <c r="AH2" s="10" t="inlineStr"/>
-      <c r="AI2" s="10" t="inlineStr"/>
-      <c r="AJ2" s="10" t="inlineStr"/>
-      <c r="AK2" s="10" t="inlineStr"/>
-      <c r="AL2" s="10" t="inlineStr"/>
-      <c r="AM2" s="10" t="inlineStr"/>
-      <c r="AN2" s="10" t="inlineStr"/>
-      <c r="AO2" s="10" t="inlineStr"/>
-      <c r="AP2" s="10" t="inlineStr"/>
-      <c r="AQ2" s="10" t="inlineStr"/>
-      <c r="AR2" s="10" t="inlineStr"/>
-      <c r="AS2" s="10" t="inlineStr"/>
-      <c r="AT2" s="10" t="inlineStr"/>
-      <c r="AU2" s="10" t="inlineStr"/>
-      <c r="AV2" s="10" t="inlineStr"/>
-      <c r="AW2" s="10" t="inlineStr"/>
-      <c r="AX2" s="10" t="inlineStr"/>
-      <c r="AY2" s="10" t="inlineStr"/>
-      <c r="AZ2" s="10" t="inlineStr"/>
-      <c r="BA2" s="10" t="inlineStr"/>
-      <c r="BB2" s="10" t="inlineStr"/>
-      <c r="BC2" s="10" t="inlineStr"/>
-      <c r="BD2" s="10" t="inlineStr"/>
-      <c r="BE2" s="10" t="inlineStr"/>
-      <c r="BF2" s="10" t="inlineStr"/>
-      <c r="BG2" s="10" t="inlineStr"/>
-      <c r="BH2" s="10" t="inlineStr"/>
-      <c r="BI2" s="10" t="inlineStr"/>
-      <c r="BJ2" s="10" t="inlineStr"/>
-      <c r="BK2" s="10" t="inlineStr"/>
+      <c r="A2" s="8" t="inlineStr"/>
+      <c r="B2" s="8" t="inlineStr"/>
+      <c r="C2" s="8" t="inlineStr"/>
+      <c r="D2" s="8" t="inlineStr"/>
+      <c r="E2" s="8" t="inlineStr"/>
+      <c r="F2" s="8" t="inlineStr"/>
+      <c r="G2" s="8" t="inlineStr"/>
+      <c r="H2" s="8" t="inlineStr"/>
+      <c r="I2" s="8" t="inlineStr"/>
+      <c r="J2" s="8" t="inlineStr"/>
+      <c r="K2" s="8" t="inlineStr"/>
+      <c r="L2" s="8" t="inlineStr"/>
+      <c r="M2" s="8" t="inlineStr"/>
+      <c r="N2" s="8" t="inlineStr"/>
+      <c r="O2" s="8" t="inlineStr"/>
+      <c r="P2" s="8" t="inlineStr"/>
+      <c r="Q2" s="8" t="inlineStr"/>
+      <c r="R2" s="8" t="inlineStr"/>
+      <c r="S2" s="8" t="inlineStr"/>
+      <c r="T2" s="8" t="inlineStr"/>
+      <c r="U2" s="8" t="inlineStr"/>
+      <c r="V2" s="8" t="inlineStr"/>
+      <c r="W2" s="8" t="inlineStr"/>
+      <c r="X2" s="8" t="inlineStr"/>
+      <c r="Y2" s="8" t="inlineStr"/>
+      <c r="Z2" s="8" t="inlineStr"/>
+      <c r="AA2" s="8" t="inlineStr"/>
+      <c r="AB2" s="8" t="inlineStr"/>
+      <c r="AC2" s="8" t="inlineStr"/>
+      <c r="AD2" s="8" t="inlineStr"/>
+      <c r="AE2" s="8" t="inlineStr"/>
+      <c r="AF2" s="8" t="inlineStr"/>
+      <c r="AG2" s="8" t="inlineStr"/>
+      <c r="AH2" s="8" t="inlineStr"/>
+      <c r="AI2" s="8" t="inlineStr"/>
+      <c r="AJ2" s="8" t="inlineStr"/>
+      <c r="AK2" s="8" t="inlineStr"/>
+      <c r="AL2" s="8" t="inlineStr"/>
+      <c r="AM2" s="8" t="inlineStr"/>
+      <c r="AN2" s="8" t="inlineStr"/>
+      <c r="AO2" s="8" t="inlineStr"/>
+      <c r="AP2" s="8" t="inlineStr"/>
+      <c r="AQ2" s="8" t="inlineStr"/>
+      <c r="AR2" s="8" t="inlineStr"/>
+      <c r="AS2" s="8" t="inlineStr"/>
+      <c r="AT2" s="8" t="inlineStr"/>
+      <c r="AU2" s="8" t="inlineStr"/>
+      <c r="AV2" s="8" t="inlineStr"/>
+      <c r="AW2" s="8" t="inlineStr"/>
+      <c r="AX2" s="8" t="inlineStr"/>
+      <c r="AY2" s="8" t="inlineStr"/>
+      <c r="AZ2" s="8" t="inlineStr"/>
+      <c r="BA2" s="8" t="inlineStr"/>
+      <c r="BB2" s="8" t="inlineStr"/>
+      <c r="BC2" s="8" t="inlineStr"/>
+      <c r="BD2" s="8" t="inlineStr"/>
+      <c r="BE2" s="8" t="inlineStr"/>
+      <c r="BF2" s="8" t="inlineStr"/>
+      <c r="BG2" s="8" t="inlineStr"/>
+      <c r="BH2" s="8" t="inlineStr"/>
+      <c r="BI2" s="8" t="inlineStr"/>
+      <c r="BJ2" s="8" t="inlineStr"/>
+      <c r="BK2" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:BK2"/>
@@ -2197,69 +2069,69 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr"/>
-      <c r="B2" s="10" t="inlineStr"/>
-      <c r="C2" s="10" t="inlineStr"/>
-      <c r="D2" s="10" t="inlineStr"/>
-      <c r="E2" s="10" t="inlineStr"/>
-      <c r="F2" s="10" t="inlineStr"/>
-      <c r="G2" s="10" t="inlineStr"/>
-      <c r="H2" s="10" t="inlineStr"/>
-      <c r="I2" s="10" t="inlineStr"/>
-      <c r="J2" s="10" t="inlineStr"/>
-      <c r="K2" s="10" t="inlineStr"/>
-      <c r="L2" s="10" t="inlineStr"/>
-      <c r="M2" s="10" t="inlineStr"/>
-      <c r="N2" s="10" t="inlineStr"/>
-      <c r="O2" s="10" t="inlineStr"/>
-      <c r="P2" s="10" t="inlineStr"/>
-      <c r="Q2" s="10" t="inlineStr"/>
-      <c r="R2" s="10" t="inlineStr"/>
-      <c r="S2" s="10" t="inlineStr"/>
-      <c r="T2" s="10" t="inlineStr"/>
-      <c r="U2" s="10" t="inlineStr"/>
-      <c r="V2" s="10" t="inlineStr"/>
-      <c r="W2" s="10" t="inlineStr"/>
-      <c r="X2" s="10" t="inlineStr"/>
-      <c r="Y2" s="10" t="inlineStr"/>
-      <c r="Z2" s="10" t="inlineStr"/>
-      <c r="AA2" s="10" t="inlineStr"/>
-      <c r="AB2" s="10" t="inlineStr"/>
-      <c r="AC2" s="10" t="inlineStr"/>
-      <c r="AD2" s="10" t="inlineStr"/>
-      <c r="AE2" s="10" t="inlineStr"/>
-      <c r="AF2" s="10" t="inlineStr"/>
-      <c r="AG2" s="10" t="inlineStr"/>
-      <c r="AH2" s="10" t="inlineStr"/>
-      <c r="AI2" s="10" t="inlineStr"/>
-      <c r="AJ2" s="10" t="inlineStr"/>
-      <c r="AK2" s="10" t="inlineStr"/>
-      <c r="AL2" s="10" t="inlineStr"/>
-      <c r="AM2" s="10" t="inlineStr"/>
-      <c r="AN2" s="10" t="inlineStr"/>
-      <c r="AO2" s="10" t="inlineStr"/>
-      <c r="AP2" s="10" t="inlineStr"/>
-      <c r="AQ2" s="10" t="inlineStr"/>
-      <c r="AR2" s="10" t="inlineStr"/>
-      <c r="AS2" s="10" t="inlineStr"/>
-      <c r="AT2" s="10" t="inlineStr"/>
-      <c r="AU2" s="10" t="inlineStr"/>
-      <c r="AV2" s="10" t="inlineStr"/>
-      <c r="AW2" s="10" t="inlineStr"/>
-      <c r="AX2" s="10" t="inlineStr"/>
-      <c r="AY2" s="10" t="inlineStr"/>
-      <c r="AZ2" s="10" t="inlineStr"/>
-      <c r="BA2" s="10" t="inlineStr"/>
-      <c r="BB2" s="10" t="inlineStr"/>
-      <c r="BC2" s="10" t="inlineStr"/>
-      <c r="BD2" s="10" t="inlineStr"/>
-      <c r="BE2" s="10" t="inlineStr"/>
-      <c r="BF2" s="10" t="inlineStr"/>
-      <c r="BG2" s="10" t="inlineStr"/>
-      <c r="BH2" s="10" t="inlineStr"/>
-      <c r="BI2" s="10" t="inlineStr"/>
-      <c r="BJ2" s="10" t="inlineStr"/>
-      <c r="BK2" s="10" t="inlineStr"/>
+      <c r="A2" s="8" t="inlineStr"/>
+      <c r="B2" s="8" t="inlineStr"/>
+      <c r="C2" s="8" t="inlineStr"/>
+      <c r="D2" s="8" t="inlineStr"/>
+      <c r="E2" s="8" t="inlineStr"/>
+      <c r="F2" s="8" t="inlineStr"/>
+      <c r="G2" s="8" t="inlineStr"/>
+      <c r="H2" s="8" t="inlineStr"/>
+      <c r="I2" s="8" t="inlineStr"/>
+      <c r="J2" s="8" t="inlineStr"/>
+      <c r="K2" s="8" t="inlineStr"/>
+      <c r="L2" s="8" t="inlineStr"/>
+      <c r="M2" s="8" t="inlineStr"/>
+      <c r="N2" s="8" t="inlineStr"/>
+      <c r="O2" s="8" t="inlineStr"/>
+      <c r="P2" s="8" t="inlineStr"/>
+      <c r="Q2" s="8" t="inlineStr"/>
+      <c r="R2" s="8" t="inlineStr"/>
+      <c r="S2" s="8" t="inlineStr"/>
+      <c r="T2" s="8" t="inlineStr"/>
+      <c r="U2" s="8" t="inlineStr"/>
+      <c r="V2" s="8" t="inlineStr"/>
+      <c r="W2" s="8" t="inlineStr"/>
+      <c r="X2" s="8" t="inlineStr"/>
+      <c r="Y2" s="8" t="inlineStr"/>
+      <c r="Z2" s="8" t="inlineStr"/>
+      <c r="AA2" s="8" t="inlineStr"/>
+      <c r="AB2" s="8" t="inlineStr"/>
+      <c r="AC2" s="8" t="inlineStr"/>
+      <c r="AD2" s="8" t="inlineStr"/>
+      <c r="AE2" s="8" t="inlineStr"/>
+      <c r="AF2" s="8" t="inlineStr"/>
+      <c r="AG2" s="8" t="inlineStr"/>
+      <c r="AH2" s="8" t="inlineStr"/>
+      <c r="AI2" s="8" t="inlineStr"/>
+      <c r="AJ2" s="8" t="inlineStr"/>
+      <c r="AK2" s="8" t="inlineStr"/>
+      <c r="AL2" s="8" t="inlineStr"/>
+      <c r="AM2" s="8" t="inlineStr"/>
+      <c r="AN2" s="8" t="inlineStr"/>
+      <c r="AO2" s="8" t="inlineStr"/>
+      <c r="AP2" s="8" t="inlineStr"/>
+      <c r="AQ2" s="8" t="inlineStr"/>
+      <c r="AR2" s="8" t="inlineStr"/>
+      <c r="AS2" s="8" t="inlineStr"/>
+      <c r="AT2" s="8" t="inlineStr"/>
+      <c r="AU2" s="8" t="inlineStr"/>
+      <c r="AV2" s="8" t="inlineStr"/>
+      <c r="AW2" s="8" t="inlineStr"/>
+      <c r="AX2" s="8" t="inlineStr"/>
+      <c r="AY2" s="8" t="inlineStr"/>
+      <c r="AZ2" s="8" t="inlineStr"/>
+      <c r="BA2" s="8" t="inlineStr"/>
+      <c r="BB2" s="8" t="inlineStr"/>
+      <c r="BC2" s="8" t="inlineStr"/>
+      <c r="BD2" s="8" t="inlineStr"/>
+      <c r="BE2" s="8" t="inlineStr"/>
+      <c r="BF2" s="8" t="inlineStr"/>
+      <c r="BG2" s="8" t="inlineStr"/>
+      <c r="BH2" s="8" t="inlineStr"/>
+      <c r="BI2" s="8" t="inlineStr"/>
+      <c r="BJ2" s="8" t="inlineStr"/>
+      <c r="BK2" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:BK2"/>
@@ -2273,11 +2145,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK3"/>
+  <dimension ref="A1:BK2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -2305,8 +2177,8 @@
     <col width="34" customWidth="1" min="27" max="27"/>
     <col width="29" customWidth="1" min="28" max="28"/>
     <col width="22" customWidth="1" min="29" max="29"/>
-    <col width="21" customWidth="1" min="30" max="30"/>
-    <col width="21" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="13" customWidth="1" min="31" max="31"/>
     <col width="16" customWidth="1" min="32" max="32"/>
     <col width="10" customWidth="1" min="33" max="33"/>
     <col width="10" customWidth="1" min="34" max="34"/>
@@ -2659,16 +2531,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>NO_SAME_SIDE_CANDIDATE</t>
-        </is>
-      </c>
+      <c r="A2" s="8" t="inlineStr"/>
+      <c r="B2" s="8" t="inlineStr"/>
       <c r="C2" s="8" t="inlineStr"/>
       <c r="D2" s="8" t="inlineStr"/>
       <c r="E2" s="8" t="inlineStr"/>
@@ -2696,35 +2560,17 @@
       <c r="AA2" s="8" t="inlineStr"/>
       <c r="AB2" s="8" t="inlineStr"/>
       <c r="AC2" s="8" t="inlineStr"/>
-      <c r="AD2" s="9" t="n">
-        <v>46171.63541666666</v>
-      </c>
-      <c r="AE2" s="9" t="n">
-        <v>46171.72916666666</v>
-      </c>
-      <c r="AF2" s="8" t="n">
-        <v>4542.18</v>
-      </c>
-      <c r="AG2" s="8" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="AH2" s="8" t="n">
-        <v>4517.1</v>
-      </c>
-      <c r="AI2" s="8" t="n">
-        <v>-25.08</v>
-      </c>
+      <c r="AD2" s="8" t="inlineStr"/>
+      <c r="AE2" s="8" t="inlineStr"/>
+      <c r="AF2" s="8" t="inlineStr"/>
+      <c r="AG2" s="8" t="inlineStr"/>
+      <c r="AH2" s="8" t="inlineStr"/>
+      <c r="AI2" s="8" t="inlineStr"/>
       <c r="AJ2" s="8" t="inlineStr"/>
       <c r="AK2" s="8" t="inlineStr"/>
       <c r="AL2" s="8" t="inlineStr"/>
       <c r="AM2" s="8" t="inlineStr"/>
-      <c r="AN2" s="8" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
+      <c r="AN2" s="8" t="inlineStr"/>
       <c r="AO2" s="8" t="inlineStr"/>
       <c r="AP2" s="8" t="inlineStr"/>
       <c r="AQ2" s="8" t="inlineStr"/>
@@ -2749,99 +2595,8 @@
       <c r="BJ2" s="8" t="inlineStr"/>
       <c r="BK2" s="8" t="inlineStr"/>
     </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>NO_SAME_SIDE_CANDIDATE</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr"/>
-      <c r="D3" s="8" t="inlineStr"/>
-      <c r="E3" s="8" t="inlineStr"/>
-      <c r="F3" s="8" t="inlineStr"/>
-      <c r="G3" s="8" t="inlineStr"/>
-      <c r="H3" s="8" t="inlineStr"/>
-      <c r="I3" s="8" t="inlineStr"/>
-      <c r="J3" s="8" t="inlineStr"/>
-      <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="8" t="inlineStr"/>
-      <c r="M3" s="8" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr"/>
-      <c r="O3" s="8" t="inlineStr"/>
-      <c r="P3" s="8" t="inlineStr"/>
-      <c r="Q3" s="8" t="inlineStr"/>
-      <c r="R3" s="8" t="inlineStr"/>
-      <c r="S3" s="8" t="inlineStr"/>
-      <c r="T3" s="8" t="inlineStr"/>
-      <c r="U3" s="8" t="inlineStr"/>
-      <c r="V3" s="8" t="inlineStr"/>
-      <c r="W3" s="8" t="inlineStr"/>
-      <c r="X3" s="8" t="inlineStr"/>
-      <c r="Y3" s="8" t="inlineStr"/>
-      <c r="Z3" s="8" t="inlineStr"/>
-      <c r="AA3" s="8" t="inlineStr"/>
-      <c r="AB3" s="8" t="inlineStr"/>
-      <c r="AC3" s="8" t="inlineStr"/>
-      <c r="AD3" s="9" t="n">
-        <v>46178.91666666666</v>
-      </c>
-      <c r="AE3" s="9" t="n">
-        <v>46179.09375</v>
-      </c>
-      <c r="AF3" s="8" t="n">
-        <v>4314.33</v>
-      </c>
-      <c r="AG3" s="8" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH3" s="8" t="n">
-        <v>4363.91</v>
-      </c>
-      <c r="AI3" s="8" t="n">
-        <v>-49.58</v>
-      </c>
-      <c r="AJ3" s="8" t="inlineStr"/>
-      <c r="AK3" s="8" t="inlineStr"/>
-      <c r="AL3" s="8" t="inlineStr"/>
-      <c r="AM3" s="8" t="inlineStr"/>
-      <c r="AN3" s="8" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO3" s="8" t="inlineStr"/>
-      <c r="AP3" s="8" t="inlineStr"/>
-      <c r="AQ3" s="8" t="inlineStr"/>
-      <c r="AR3" s="8" t="inlineStr"/>
-      <c r="AS3" s="8" t="inlineStr"/>
-      <c r="AT3" s="8" t="inlineStr"/>
-      <c r="AU3" s="8" t="inlineStr"/>
-      <c r="AV3" s="8" t="inlineStr"/>
-      <c r="AW3" s="8" t="inlineStr"/>
-      <c r="AX3" s="8" t="inlineStr"/>
-      <c r="AY3" s="8" t="inlineStr"/>
-      <c r="AZ3" s="8" t="inlineStr"/>
-      <c r="BA3" s="8" t="inlineStr"/>
-      <c r="BB3" s="8" t="inlineStr"/>
-      <c r="BC3" s="8" t="inlineStr"/>
-      <c r="BD3" s="8" t="inlineStr"/>
-      <c r="BE3" s="8" t="inlineStr"/>
-      <c r="BF3" s="8" t="inlineStr"/>
-      <c r="BG3" s="8" t="inlineStr"/>
-      <c r="BH3" s="8" t="inlineStr"/>
-      <c r="BI3" s="8" t="inlineStr"/>
-      <c r="BJ3" s="8" t="inlineStr"/>
-      <c r="BK3" s="8" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BK3"/>
+  <autoFilter ref="A1:BK2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3238,69 +2993,69 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr"/>
-      <c r="B2" s="10" t="inlineStr"/>
-      <c r="C2" s="10" t="inlineStr"/>
-      <c r="D2" s="10" t="inlineStr"/>
-      <c r="E2" s="10" t="inlineStr"/>
-      <c r="F2" s="10" t="inlineStr"/>
-      <c r="G2" s="10" t="inlineStr"/>
-      <c r="H2" s="10" t="inlineStr"/>
-      <c r="I2" s="10" t="inlineStr"/>
-      <c r="J2" s="10" t="inlineStr"/>
-      <c r="K2" s="10" t="inlineStr"/>
-      <c r="L2" s="10" t="inlineStr"/>
-      <c r="M2" s="10" t="inlineStr"/>
-      <c r="N2" s="10" t="inlineStr"/>
-      <c r="O2" s="10" t="inlineStr"/>
-      <c r="P2" s="10" t="inlineStr"/>
-      <c r="Q2" s="10" t="inlineStr"/>
-      <c r="R2" s="10" t="inlineStr"/>
-      <c r="S2" s="10" t="inlineStr"/>
-      <c r="T2" s="10" t="inlineStr"/>
-      <c r="U2" s="10" t="inlineStr"/>
-      <c r="V2" s="10" t="inlineStr"/>
-      <c r="W2" s="10" t="inlineStr"/>
-      <c r="X2" s="10" t="inlineStr"/>
-      <c r="Y2" s="10" t="inlineStr"/>
-      <c r="Z2" s="10" t="inlineStr"/>
-      <c r="AA2" s="10" t="inlineStr"/>
-      <c r="AB2" s="10" t="inlineStr"/>
-      <c r="AC2" s="10" t="inlineStr"/>
-      <c r="AD2" s="10" t="inlineStr"/>
-      <c r="AE2" s="10" t="inlineStr"/>
-      <c r="AF2" s="10" t="inlineStr"/>
-      <c r="AG2" s="10" t="inlineStr"/>
-      <c r="AH2" s="10" t="inlineStr"/>
-      <c r="AI2" s="10" t="inlineStr"/>
-      <c r="AJ2" s="10" t="inlineStr"/>
-      <c r="AK2" s="10" t="inlineStr"/>
-      <c r="AL2" s="10" t="inlineStr"/>
-      <c r="AM2" s="10" t="inlineStr"/>
-      <c r="AN2" s="10" t="inlineStr"/>
-      <c r="AO2" s="10" t="inlineStr"/>
-      <c r="AP2" s="10" t="inlineStr"/>
-      <c r="AQ2" s="10" t="inlineStr"/>
-      <c r="AR2" s="10" t="inlineStr"/>
-      <c r="AS2" s="10" t="inlineStr"/>
-      <c r="AT2" s="10" t="inlineStr"/>
-      <c r="AU2" s="10" t="inlineStr"/>
-      <c r="AV2" s="10" t="inlineStr"/>
-      <c r="AW2" s="10" t="inlineStr"/>
-      <c r="AX2" s="10" t="inlineStr"/>
-      <c r="AY2" s="10" t="inlineStr"/>
-      <c r="AZ2" s="10" t="inlineStr"/>
-      <c r="BA2" s="10" t="inlineStr"/>
-      <c r="BB2" s="10" t="inlineStr"/>
-      <c r="BC2" s="10" t="inlineStr"/>
-      <c r="BD2" s="10" t="inlineStr"/>
-      <c r="BE2" s="10" t="inlineStr"/>
-      <c r="BF2" s="10" t="inlineStr"/>
-      <c r="BG2" s="10" t="inlineStr"/>
-      <c r="BH2" s="10" t="inlineStr"/>
-      <c r="BI2" s="10" t="inlineStr"/>
-      <c r="BJ2" s="10" t="inlineStr"/>
-      <c r="BK2" s="10" t="inlineStr"/>
+      <c r="A2" s="8" t="inlineStr"/>
+      <c r="B2" s="8" t="inlineStr"/>
+      <c r="C2" s="8" t="inlineStr"/>
+      <c r="D2" s="8" t="inlineStr"/>
+      <c r="E2" s="8" t="inlineStr"/>
+      <c r="F2" s="8" t="inlineStr"/>
+      <c r="G2" s="8" t="inlineStr"/>
+      <c r="H2" s="8" t="inlineStr"/>
+      <c r="I2" s="8" t="inlineStr"/>
+      <c r="J2" s="8" t="inlineStr"/>
+      <c r="K2" s="8" t="inlineStr"/>
+      <c r="L2" s="8" t="inlineStr"/>
+      <c r="M2" s="8" t="inlineStr"/>
+      <c r="N2" s="8" t="inlineStr"/>
+      <c r="O2" s="8" t="inlineStr"/>
+      <c r="P2" s="8" t="inlineStr"/>
+      <c r="Q2" s="8" t="inlineStr"/>
+      <c r="R2" s="8" t="inlineStr"/>
+      <c r="S2" s="8" t="inlineStr"/>
+      <c r="T2" s="8" t="inlineStr"/>
+      <c r="U2" s="8" t="inlineStr"/>
+      <c r="V2" s="8" t="inlineStr"/>
+      <c r="W2" s="8" t="inlineStr"/>
+      <c r="X2" s="8" t="inlineStr"/>
+      <c r="Y2" s="8" t="inlineStr"/>
+      <c r="Z2" s="8" t="inlineStr"/>
+      <c r="AA2" s="8" t="inlineStr"/>
+      <c r="AB2" s="8" t="inlineStr"/>
+      <c r="AC2" s="8" t="inlineStr"/>
+      <c r="AD2" s="8" t="inlineStr"/>
+      <c r="AE2" s="8" t="inlineStr"/>
+      <c r="AF2" s="8" t="inlineStr"/>
+      <c r="AG2" s="8" t="inlineStr"/>
+      <c r="AH2" s="8" t="inlineStr"/>
+      <c r="AI2" s="8" t="inlineStr"/>
+      <c r="AJ2" s="8" t="inlineStr"/>
+      <c r="AK2" s="8" t="inlineStr"/>
+      <c r="AL2" s="8" t="inlineStr"/>
+      <c r="AM2" s="8" t="inlineStr"/>
+      <c r="AN2" s="8" t="inlineStr"/>
+      <c r="AO2" s="8" t="inlineStr"/>
+      <c r="AP2" s="8" t="inlineStr"/>
+      <c r="AQ2" s="8" t="inlineStr"/>
+      <c r="AR2" s="8" t="inlineStr"/>
+      <c r="AS2" s="8" t="inlineStr"/>
+      <c r="AT2" s="8" t="inlineStr"/>
+      <c r="AU2" s="8" t="inlineStr"/>
+      <c r="AV2" s="8" t="inlineStr"/>
+      <c r="AW2" s="8" t="inlineStr"/>
+      <c r="AX2" s="8" t="inlineStr"/>
+      <c r="AY2" s="8" t="inlineStr"/>
+      <c r="AZ2" s="8" t="inlineStr"/>
+      <c r="BA2" s="8" t="inlineStr"/>
+      <c r="BB2" s="8" t="inlineStr"/>
+      <c r="BC2" s="8" t="inlineStr"/>
+      <c r="BD2" s="8" t="inlineStr"/>
+      <c r="BE2" s="8" t="inlineStr"/>
+      <c r="BF2" s="8" t="inlineStr"/>
+      <c r="BG2" s="8" t="inlineStr"/>
+      <c r="BH2" s="8" t="inlineStr"/>
+      <c r="BI2" s="8" t="inlineStr"/>
+      <c r="BJ2" s="8" t="inlineStr"/>
+      <c r="BK2" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:BK2"/>
@@ -3314,16 +3069,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3364,152 +3119,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>bt</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="C2" s="10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="10" t="n">
-        <v>-49.58</v>
-      </c>
-      <c r="F2" s="11" t="n">
-        <v>46178.91666666666</v>
-      </c>
-      <c r="G2" s="11" t="n">
-        <v>46178.91666666666</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>bt</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D3" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="10" t="n">
-        <v>-25.08</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>46171.63541666666</v>
-      </c>
-      <c r="G3" s="11" t="n">
-        <v>46171.63541666666</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>bt_gap</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>NO_SAME_SIDE_CANDIDATE</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" s="10" t="n">
-        <v>-74.66</v>
-      </c>
-      <c r="F4" s="11" t="n">
-        <v>46171.63541666666</v>
-      </c>
-      <c r="G4" s="11" t="n">
-        <v>46178.91666666666</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>bt_s14_family</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>-49.58</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>46178.91666666666</v>
-      </c>
-      <c r="G5" s="11" t="n">
-        <v>46178.91666666666</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>bt_s14_family</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>-25.08</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>46171.63541666666</v>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>46171.63541666666</v>
-      </c>
+      <c r="A2" s="8" t="inlineStr"/>
+      <c r="B2" s="8" t="inlineStr"/>
+      <c r="C2" s="8" t="inlineStr"/>
+      <c r="D2" s="8" t="inlineStr"/>
+      <c r="E2" s="8" t="inlineStr"/>
+      <c r="F2" s="8" t="inlineStr"/>
+      <c r="G2" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:G2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>